--- a/Hackathon_refinement-main/PHASE_2/INPUT/TIO2_Sprint_Intelligence_v5_final.xlsx
+++ b/Hackathon_refinement-main/PHASE_2/INPUT/TIO2_Sprint_Intelligence_v5_final.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Project_Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Team" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sprint_Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Work_Items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Blockers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Lists" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint_Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work_Items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blockers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -146,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,6 +179,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.6640625" customWidth="1" style="15" min="1" max="1"/>
@@ -911,15 +915,21 @@
       <c r="S3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="6" t="n"/>
+      <c r="T3" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="U3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V3" s="6" t="n"/>
+      <c r="V3" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X3" s="6" t="n"/>
+      <c r="X3" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="4" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A4" s="5" t="inlineStr">
@@ -995,15 +1005,21 @@
       <c r="S4" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="T4" s="6" t="n"/>
+      <c r="T4" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="U4" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="6" t="n"/>
+      <c r="V4" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W4" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="X4" s="6" t="n"/>
+      <c r="X4" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="5" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A5" s="5" t="inlineStr">
@@ -1079,15 +1095,21 @@
       <c r="S5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="6" t="n"/>
+      <c r="T5" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="U5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V5" s="6" t="n"/>
+      <c r="V5" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X5" s="6" t="n"/>
+      <c r="X5" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A6" s="5" t="inlineStr">
@@ -1163,15 +1185,21 @@
       <c r="S6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" s="6" t="n"/>
+      <c r="T6" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="6" t="n"/>
+      <c r="V6" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" s="6" t="n"/>
+      <c r="X6" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="7" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1245,17 +1273,23 @@
         <v>0.7</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T7" s="6" t="n"/>
+        <v>0.95</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0.65</v>
+      </c>
       <c r="U7" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="V7" s="6" t="n"/>
+      <c r="V7" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W7" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="X7" s="6" t="n"/>
+      <c r="X7" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A8" s="5" t="inlineStr">
@@ -1329,17 +1363,23 @@
         <v>0.4</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T8" s="6" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U8" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="V8" s="6" t="n"/>
+      <c r="V8" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W8" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="X8" s="6" t="n"/>
+      <c r="X8" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A9" s="5" t="inlineStr">
@@ -1415,15 +1455,21 @@
       <c r="S9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n"/>
+      <c r="T9" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="6" t="n"/>
+      <c r="V9" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X9" s="6" t="n"/>
+      <c r="X9" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="10" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A10" s="5" t="inlineStr">
@@ -1499,15 +1545,21 @@
       <c r="S10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="6" t="n"/>
+      <c r="T10" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="U10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="6" t="n"/>
+      <c r="V10" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="11" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A11" s="5" t="inlineStr">
@@ -1583,28 +1635,125 @@
       <c r="S11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="6" t="n"/>
+      <c r="T11" s="6" t="n">
+        <v>0.55</v>
+      </c>
       <c r="U11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="6" t="n"/>
+      <c r="V11" s="6" t="n">
+        <v>0.9</v>
+      </c>
       <c r="W11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="X11" s="6" t="n"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1" s="15">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="X11" s="6" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Nisha Ramanathan</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Junior OTA / Firmware Engineer</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>OTA Firmware Update Mechanisms</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>L4-Beginner</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Manifest &amp; Delta Packaging</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>L4-Beginner</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Regression &amp; Integration Testing</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>L4-Beginner</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" s="15"/>
+    <row r="14" ht="14.25" customHeight="1" s="15">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Skill Levels: L1=Expert  |  L2=Advanced  |  L3=Intermediate  |  L4=Beginner</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" s="15">
-      <c r="A14" s="9" t="n"/>
-    </row>
     <row r="15" ht="14.25" customHeight="1" s="15">
-      <c r="A15" s="10" t="n"/>
+      <c r="A15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1890,7 +2039,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>OTA Updates — delta packaging, session manager, rollback, manifest validation. BLK-004 resolution critical. TLS 1.3 + IDS carry-overs from S5.</t>
+          <t>OTA Updates — BLK-006 blocks critical-path WI-053 in current Sprint 6. Requirement changes increased OTA scope; Ravi is overloaded and Nisha is ramping up with KT.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5209,13 +5358,13 @@
         <v>28</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M47" s="11" t="n">
         <v>0</v>
@@ -5227,10 +5376,14 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Requirement Change</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="39" customHeight="1" s="15">
       <c r="A48" s="2" t="inlineStr">
@@ -5413,13 +5566,13 @@
         <v>16</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M50" s="11" t="n">
         <v>0</v>
@@ -5431,10 +5584,14 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Requirement Change</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="39" customHeight="1" s="15">
       <c r="A51" s="2" t="inlineStr">
@@ -5668,7 +5825,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Meena Balasubramanian</t>
+          <t>Ravi Chandran</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -5685,13 +5842,13 @@
         <v>36</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="M54" s="11" t="n">
         <v>0</v>
@@ -5703,10 +5860,14 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Requirement Change</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="26.25" customHeight="1" s="15">
       <c r="A55" s="2" t="inlineStr">
@@ -5736,7 +5897,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Meena Balasubramanian</t>
+          <t>Nisha Ramanathan</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -5753,13 +5914,13 @@
         <v>32</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="M55" s="11" t="n">
         <v>0</v>
@@ -5771,10 +5932,14 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Requirement Change</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="26.25" customHeight="1" s="15">
       <c r="A56" s="2" t="inlineStr">
@@ -5804,7 +5969,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Meena Balasubramanian</t>
+          <t>Priya Meenakshi</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -5821,13 +5986,13 @@
         <v>24</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="M56" s="11" t="n">
         <v>0</v>
@@ -5839,10 +6004,14 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Customer Request</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="15">
       <c r="A57" s="2" t="inlineStr">
@@ -6008,7 +6177,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Meena Balasubramanian</t>
+          <t>Ravi Chandran</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6025,13 +6194,13 @@
         <v>16</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M59" s="11" t="n">
         <v>0</v>
@@ -7767,7 +7936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="25" customWidth="1" style="15" min="1" max="1"/>
@@ -8060,7 +8229,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8078,10 +8247,8 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
+      <c r="I6" s="17" t="n">
+        <v>46227</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -8095,7 +8262,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Daimler API credentials for backend OTA integration not provisioned. Blocking WI-056/058. Open.</t>
+          <t>Daimler API credentials provisioned and prior Sprint 5 integration issue closed.</t>
         </is>
       </c>
     </row>
@@ -8161,8 +8328,66 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BLK-006</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WI-053</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>WI-053, WI-057, WI-062</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ravi Chandran</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>46230</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>External Team Dependency</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Current Sprint 6 blocker on critical-path OTA Session Manager (WI-053). Blocks downstream OTA validation/integration work. Target resolution 03-Aug-2026; no blocker is assumed for future sprints.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
